--- a/results/UniteD-SRL - run.xlsx
+++ b/results/UniteD-SRL - run.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\vito\SRL\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A2E73F-E0C0-4A0E-A2A3-69D37B8BA1DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF22AB8D-5115-4C14-850D-AFAD3BA3C1C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8190" yWindow="165" windowWidth="22275" windowHeight="10365" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="42165" yWindow="2850" windowWidth="22275" windowHeight="10365" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dependency-based" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="21">
   <si>
     <t>English</t>
   </si>
@@ -97,6 +97,9 @@
   </si>
   <si>
     <t>google/gemma-3-1b-it</t>
+  </si>
+  <si>
+    <t>ONESHOT</t>
   </si>
 </sst>
 </file>
@@ -224,9 +227,6 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -246,6 +246,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -508,32 +511,32 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
+      <c r="I1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
       <c r="L1" s="2"/>
-      <c r="M1" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="Q1" s="15" t="s">
+      <c r="M1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="Q1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="U1" s="15" t="s">
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="U1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="V1" s="16"/>
-      <c r="W1" s="16"/>
-      <c r="Y1" s="15" t="s">
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="Y1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="Z1" s="16"/>
-      <c r="AA1" s="16"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
       <c r="AB1" s="2"/>
       <c r="AC1" s="2"/>
       <c r="AD1" s="2"/>
@@ -553,44 +556,44 @@
       <c r="AR1" s="2"/>
     </row>
     <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
       <c r="L2" s="2"/>
-      <c r="M2" s="18" t="s">
+      <c r="M2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="Q2" s="18" t="s">
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="Q2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="U2" s="18" t="s">
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="U2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="Y2" s="18" t="s">
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="Y2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
       <c r="AD2" s="2"/>
@@ -610,7 +613,7 @@
       <c r="AR2" s="2"/>
     </row>
     <row r="3" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="16"/>
+      <c r="A3" s="15"/>
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
@@ -698,22 +701,22 @@
       <c r="A4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="C4" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="b">
+      <c r="B4" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C4" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="13" t="b">
         <v>0</v>
       </c>
       <c r="H4" s="1"/>
@@ -786,22 +789,22 @@
     </row>
     <row r="5" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
-      <c r="B5" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="C5" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D5" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14" t="b">
+      <c r="B5" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="13" t="b">
         <v>0</v>
       </c>
       <c r="H5" s="1"/>
@@ -874,22 +877,22 @@
     </row>
     <row r="6" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
-      <c r="B6" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="C6" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D6" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="14" t="b">
+      <c r="B6" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C6" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="13" t="b">
         <v>0</v>
       </c>
       <c r="H6" s="1"/>
@@ -962,22 +965,22 @@
     </row>
     <row r="7" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
-      <c r="B7" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="C7" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D7" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="14" t="b">
+      <c r="B7" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C7" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="13" t="b">
         <v>0</v>
       </c>
       <c r="H7" s="1"/>
@@ -1050,22 +1053,22 @@
     </row>
     <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
-      <c r="B8" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="C8" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D8" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="14" t="b">
+      <c r="B8" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C8" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="13" t="b">
         <v>1</v>
       </c>
       <c r="H8" s="1"/>
@@ -1138,22 +1141,22 @@
     </row>
     <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5"/>
-      <c r="B9" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="C9" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D9" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="14" t="b">
+      <c r="B9" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C9" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="13" t="b">
         <v>1</v>
       </c>
       <c r="H9" s="1"/>
@@ -1228,22 +1231,22 @@
       <c r="A10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="C10" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="14" t="b">
+      <c r="B10" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C10" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="13" t="b">
         <v>0</v>
       </c>
       <c r="H10" s="1"/>
@@ -1316,22 +1319,22 @@
     </row>
     <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9"/>
-      <c r="B11" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="C11" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D11" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="14" t="b">
+      <c r="B11" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D11" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="13" t="b">
         <v>0</v>
       </c>
       <c r="I11">
@@ -1385,22 +1388,22 @@
     </row>
     <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9"/>
-      <c r="B12" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="C12" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D12" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="14" t="b">
+      <c r="B12" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C12" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13" t="b">
         <v>0</v>
       </c>
       <c r="I12">
@@ -1454,22 +1457,22 @@
     </row>
     <row r="13" spans="1:44" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9"/>
-      <c r="B13" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="C13" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D13" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="14" t="b">
+      <c r="B13" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C13" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="13" t="b">
         <v>0</v>
       </c>
       <c r="I13" s="6">
@@ -1523,22 +1526,22 @@
     </row>
     <row r="14" spans="1:44" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9"/>
-      <c r="B14" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="C14" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D14" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" s="14" t="b">
+      <c r="B14" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C14" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="13" t="b">
         <v>1</v>
       </c>
       <c r="I14" s="6">
@@ -1592,22 +1595,22 @@
     </row>
     <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9"/>
-      <c r="B15" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="C15" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="14" t="b">
+      <c r="B15" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C15" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="13" t="b">
         <v>1</v>
       </c>
       <c r="I15" s="6">
@@ -1663,110 +1666,282 @@
       <c r="A16" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="C16" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D16" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="S16" s="10"/>
-      <c r="W16" s="10"/>
-      <c r="Y16" s="6" t="e">
+      <c r="B16" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="6">
+        <v>0</v>
+      </c>
+      <c r="J16" s="6">
+        <v>0</v>
+      </c>
+      <c r="K16" s="7">
+        <v>0</v>
+      </c>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6">
+        <v>0</v>
+      </c>
+      <c r="N16" s="6">
+        <v>0</v>
+      </c>
+      <c r="O16" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="6">
+        <v>0</v>
+      </c>
+      <c r="R16" s="6">
+        <v>0</v>
+      </c>
+      <c r="S16" s="7">
+        <v>0</v>
+      </c>
+      <c r="U16" s="6">
+        <v>0</v>
+      </c>
+      <c r="V16" s="6">
+        <v>0</v>
+      </c>
+      <c r="W16" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="6">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z16" s="6" t="e">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="6">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA16" s="7" t="e">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="7">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="12"/>
-      <c r="B17" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="C17" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D17" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="14" t="b">
+      <c r="B17" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="13" t="b">
         <v>1</v>
       </c>
       <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
-      <c r="W17" s="13"/>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="6" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z17" s="6" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA17" s="7" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+      <c r="I17" s="6">
+        <v>17.18</v>
+      </c>
+      <c r="J17" s="6">
+        <v>7.58</v>
+      </c>
+      <c r="K17" s="7">
+        <v>10.52</v>
+      </c>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6">
+        <v>10.039999999999999</v>
+      </c>
+      <c r="N17" s="6">
+        <v>3.77</v>
+      </c>
+      <c r="O17" s="7">
+        <v>5.48</v>
+      </c>
+      <c r="Q17" s="6">
+        <v>19.420000000000002</v>
+      </c>
+      <c r="R17" s="6">
+        <v>8.6</v>
+      </c>
+      <c r="S17" s="7">
+        <v>11.92</v>
+      </c>
+      <c r="U17" s="6">
+        <v>13.54</v>
+      </c>
+      <c r="V17" s="6">
+        <v>6.31</v>
+      </c>
+      <c r="W17" s="7">
+        <v>8.61</v>
+      </c>
+      <c r="Y17" s="6">
+        <f t="shared" ref="Y17:Y19" si="6">AVERAGE(I17,M17,Q17,U17)</f>
+        <v>15.045</v>
+      </c>
+      <c r="Z17" s="6">
+        <f t="shared" ref="Z17:Z19" si="7">AVERAGE(J17,N17,R17,V17)</f>
+        <v>6.5649999999999995</v>
+      </c>
+      <c r="AA17" s="7">
+        <f t="shared" ref="AA17:AA19" si="8">AVERAGE(K17,O17,S17,W17)</f>
+        <v>9.1325000000000003</v>
       </c>
       <c r="AB17" s="2"/>
       <c r="AC17" s="2"/>
       <c r="AD17" s="2"/>
       <c r="AE17" s="1"/>
-      <c r="AF17" s="15"/>
-      <c r="AG17" s="16"/>
-      <c r="AH17" s="16"/>
-      <c r="AI17" s="16"/>
-      <c r="AJ17" s="16"/>
-      <c r="AK17" s="16"/>
+      <c r="AF17" s="14"/>
+      <c r="AG17" s="15"/>
+      <c r="AH17" s="15"/>
+      <c r="AI17" s="15"/>
+      <c r="AJ17" s="15"/>
+      <c r="AK17" s="15"/>
       <c r="AL17" s="1"/>
-      <c r="AM17" s="15"/>
-      <c r="AN17" s="16"/>
-      <c r="AO17" s="16"/>
-      <c r="AP17" s="16"/>
-      <c r="AQ17" s="16"/>
-      <c r="AR17" s="16"/>
+      <c r="AM17" s="14"/>
+      <c r="AN17" s="15"/>
+      <c r="AO17" s="15"/>
+      <c r="AP17" s="15"/>
+      <c r="AQ17" s="15"/>
+      <c r="AR17" s="15"/>
     </row>
-    <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" s="6">
+        <v>0</v>
+      </c>
+      <c r="J18" s="6">
+        <v>0</v>
+      </c>
+      <c r="K18" s="7">
+        <v>0</v>
+      </c>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6">
+        <v>0</v>
+      </c>
+      <c r="N18" s="6">
+        <v>0</v>
+      </c>
+      <c r="O18" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="6">
+        <v>0</v>
+      </c>
+      <c r="R18" s="6">
+        <v>0</v>
+      </c>
+      <c r="S18" s="7">
+        <v>0</v>
+      </c>
+      <c r="U18" s="6">
+        <v>0</v>
+      </c>
+      <c r="V18" s="6">
+        <v>0</v>
+      </c>
+      <c r="W18" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AA18" s="7">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="7"/>
+      <c r="Q19" s="6"/>
+      <c r="R19" s="6"/>
+      <c r="S19" s="7"/>
+      <c r="U19" s="6"/>
+      <c r="V19" s="6"/>
+      <c r="W19" s="7"/>
+      <c r="Y19" s="6" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z19" s="6" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA19" s="7" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
     <row r="20" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="21" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2767,32 +2942,32 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
+      <c r="I1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
       <c r="L1" s="2"/>
-      <c r="M1" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="Q1" s="15" t="s">
+      <c r="M1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="Q1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="U1" s="15" t="s">
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="U1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="V1" s="16"/>
-      <c r="W1" s="16"/>
-      <c r="Y1" s="15" t="s">
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="Y1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="Z1" s="16"/>
-      <c r="AA1" s="16"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
       <c r="AB1" s="2"/>
       <c r="AC1" s="2"/>
       <c r="AD1" s="2"/>
@@ -2812,44 +2987,44 @@
       <c r="AR1" s="2"/>
     </row>
     <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
       <c r="L2" s="2"/>
-      <c r="M2" s="18" t="s">
+      <c r="M2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="Q2" s="18" t="s">
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="Q2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="U2" s="18" t="s">
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="U2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="Y2" s="18" t="s">
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="Y2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
       <c r="AD2" s="2"/>
@@ -2869,7 +3044,7 @@
       <c r="AR2" s="2"/>
     </row>
     <row r="3" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="16"/>
+      <c r="A3" s="15"/>
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
@@ -2957,22 +3132,22 @@
       <c r="A4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="C4" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="14" t="b">
+      <c r="B4" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C4" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="13" t="b">
         <v>0</v>
       </c>
       <c r="H4" s="1"/>
@@ -3045,22 +3220,22 @@
     </row>
     <row r="5" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
-      <c r="B5" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="C5" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D5" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14" t="b">
+      <c r="B5" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="13" t="b">
         <v>0</v>
       </c>
       <c r="H5" s="1"/>
@@ -3133,22 +3308,22 @@
     </row>
     <row r="6" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
-      <c r="B6" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="C6" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D6" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="14" t="b">
+      <c r="B6" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C6" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="13" t="b">
         <v>0</v>
       </c>
       <c r="H6" s="1"/>
@@ -3221,22 +3396,22 @@
     </row>
     <row r="7" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
-      <c r="B7" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="C7" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D7" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="14" t="b">
+      <c r="B7" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C7" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="13" t="b">
         <v>0</v>
       </c>
       <c r="H7" s="1"/>
@@ -3246,11 +3421,11 @@
       <c r="J7" s="6">
         <v>66.98</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="6">
         <v>73.52</v>
       </c>
       <c r="L7" s="6"/>
-      <c r="M7" s="6">
+      <c r="M7" s="7">
         <v>78</v>
       </c>
       <c r="N7" s="6">
@@ -3309,22 +3484,22 @@
     </row>
     <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
-      <c r="B8" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="C8" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D8" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="14" t="b">
+      <c r="B8" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C8" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="13" t="b">
         <v>1</v>
       </c>
       <c r="H8" s="1"/>
@@ -3397,22 +3572,22 @@
     </row>
     <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5"/>
-      <c r="B9" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="C9" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D9" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="14" t="b">
+      <c r="B9" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C9" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="13" t="b">
         <v>1</v>
       </c>
       <c r="H9" s="1"/>
@@ -3487,22 +3662,22 @@
       <c r="A10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="C10" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="14" t="b">
+      <c r="B10" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C10" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D10" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="13" t="b">
         <v>0</v>
       </c>
       <c r="H10" s="1"/>
@@ -3575,22 +3750,22 @@
     </row>
     <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9"/>
-      <c r="B11" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="C11" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D11" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="14" t="b">
+      <c r="B11" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D11" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="13" t="b">
         <v>0</v>
       </c>
       <c r="I11">
@@ -3630,7 +3805,7 @@
         <v>15.7</v>
       </c>
       <c r="Y11" s="6">
-        <f t="shared" ref="Y11:AA17" si="1">AVERAGE(I11,M11,Q11,U11)</f>
+        <f t="shared" ref="Y11:AA19" si="1">AVERAGE(I11,M11,Q11,U11)</f>
         <v>56.392499999999998</v>
       </c>
       <c r="Z11" s="6">
@@ -3644,22 +3819,22 @@
     </row>
     <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9"/>
-      <c r="B12" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="C12" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D12" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="14" t="b">
+      <c r="B12" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C12" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13" t="b">
         <v>0</v>
       </c>
       <c r="I12">
@@ -3713,22 +3888,22 @@
     </row>
     <row r="13" spans="1:44" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9"/>
-      <c r="B13" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="C13" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D13" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G13" s="14" t="b">
+      <c r="B13" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C13" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="13" t="b">
         <v>0</v>
       </c>
       <c r="I13" s="6">
@@ -3782,22 +3957,22 @@
     </row>
     <row r="14" spans="1:44" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9"/>
-      <c r="B14" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="C14" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D14" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G14" s="14" t="b">
+      <c r="B14" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C14" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14" s="13" t="b">
         <v>1</v>
       </c>
       <c r="I14" s="6">
@@ -3851,22 +4026,22 @@
     </row>
     <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9"/>
-      <c r="B15" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="C15" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F15" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G15" s="14" t="b">
+      <c r="B15" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C15" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="13" t="b">
         <v>1</v>
       </c>
       <c r="I15" s="6">
@@ -3922,110 +4097,308 @@
       <c r="A16" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="C16" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D16" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="S16" s="10"/>
-      <c r="W16" s="10"/>
-      <c r="Y16" s="6" t="e">
+      <c r="B16" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="6">
+        <v>0</v>
+      </c>
+      <c r="J16" s="6">
+        <v>0</v>
+      </c>
+      <c r="K16" s="7">
+        <v>0</v>
+      </c>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6">
+        <v>0</v>
+      </c>
+      <c r="N16" s="6">
+        <v>0</v>
+      </c>
+      <c r="O16" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="6">
+        <v>0</v>
+      </c>
+      <c r="R16" s="6">
+        <v>0</v>
+      </c>
+      <c r="S16" s="7">
+        <v>0</v>
+      </c>
+      <c r="U16" s="6">
+        <v>0</v>
+      </c>
+      <c r="V16" s="6">
+        <v>0</v>
+      </c>
+      <c r="W16" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z16" s="6" t="e">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA16" s="7" t="e">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="7">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="12"/>
-      <c r="B17" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="C17" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D17" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F17" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="14" t="b">
+      <c r="B17" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="13" t="b">
         <v>1</v>
       </c>
       <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
-      <c r="W17" s="13"/>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="6" t="e">
+      <c r="I17" s="6">
+        <v>5.63</v>
+      </c>
+      <c r="J17" s="6">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="K17" s="7">
+        <v>1.91</v>
+      </c>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6">
+        <v>10.48</v>
+      </c>
+      <c r="N17" s="6">
+        <v>1.79</v>
+      </c>
+      <c r="O17" s="7">
+        <v>3.05</v>
+      </c>
+      <c r="Q17" s="6">
+        <v>6.26</v>
+      </c>
+      <c r="R17" s="6">
+        <v>1.57</v>
+      </c>
+      <c r="S17" s="7">
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="U17" s="6">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="V17" s="6">
+        <v>1.08</v>
+      </c>
+      <c r="W17" s="7">
+        <v>1.74</v>
+      </c>
+      <c r="X17" s="19"/>
+      <c r="Y17" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z17" s="6" t="e">
+        <v>6.7224999999999993</v>
+      </c>
+      <c r="Z17" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA17" s="7" t="e">
+        <v>1.3975</v>
+      </c>
+      <c r="AA17" s="7">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>2.3024999999999998</v>
       </c>
       <c r="AB17" s="2"/>
       <c r="AC17" s="2"/>
       <c r="AD17" s="2"/>
       <c r="AE17" s="1"/>
-      <c r="AF17" s="15"/>
-      <c r="AG17" s="16"/>
-      <c r="AH17" s="16"/>
-      <c r="AI17" s="16"/>
-      <c r="AJ17" s="16"/>
-      <c r="AK17" s="16"/>
+      <c r="AF17" s="14"/>
+      <c r="AG17" s="15"/>
+      <c r="AH17" s="15"/>
+      <c r="AI17" s="15"/>
+      <c r="AJ17" s="15"/>
+      <c r="AK17" s="15"/>
       <c r="AL17" s="1"/>
-      <c r="AM17" s="15"/>
-      <c r="AN17" s="16"/>
-      <c r="AO17" s="16"/>
-      <c r="AP17" s="16"/>
-      <c r="AQ17" s="16"/>
-      <c r="AR17" s="16"/>
+      <c r="AM17" s="14"/>
+      <c r="AN17" s="15"/>
+      <c r="AO17" s="15"/>
+      <c r="AP17" s="15"/>
+      <c r="AQ17" s="15"/>
+      <c r="AR17" s="15"/>
     </row>
-    <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" s="6">
+        <v>0</v>
+      </c>
+      <c r="J18" s="6">
+        <v>0</v>
+      </c>
+      <c r="K18" s="7">
+        <v>0</v>
+      </c>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6">
+        <v>0</v>
+      </c>
+      <c r="N18" s="6">
+        <v>0</v>
+      </c>
+      <c r="O18" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="6">
+        <v>0</v>
+      </c>
+      <c r="R18" s="6">
+        <v>0</v>
+      </c>
+      <c r="S18" s="7">
+        <v>0</v>
+      </c>
+      <c r="U18" s="6">
+        <v>0</v>
+      </c>
+      <c r="V18" s="6">
+        <v>0</v>
+      </c>
+      <c r="W18" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AA18" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" s="6">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="J19" s="6">
+        <v>0.21</v>
+      </c>
+      <c r="K19" s="7">
+        <v>0.38</v>
+      </c>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6">
+        <v>5.73</v>
+      </c>
+      <c r="N19" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="O19" s="7">
+        <v>1.48</v>
+      </c>
+      <c r="Q19" s="6">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="R19" s="6">
+        <v>0.48</v>
+      </c>
+      <c r="S19" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="U19" s="6">
+        <v>1.84</v>
+      </c>
+      <c r="V19" s="6">
+        <v>0.37</v>
+      </c>
+      <c r="W19" s="7">
+        <v>0.62</v>
+      </c>
+      <c r="X19" s="19"/>
+      <c r="Y19" s="6">
+        <f t="shared" si="1"/>
+        <v>2.99</v>
+      </c>
+      <c r="Z19" s="6">
+        <f t="shared" si="1"/>
+        <v>0.47750000000000004</v>
+      </c>
+      <c r="AA19" s="7">
+        <f t="shared" si="1"/>
+        <v>0.82000000000000006</v>
+      </c>
+    </row>
     <row r="20" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="21" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4983,6 +5356,13 @@
     <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="AF17:AK17"/>
+    <mergeCell ref="AM17:AR17"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="U1:W1"/>
+    <mergeCell ref="Y1:AA1"/>
+    <mergeCell ref="M1:O1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="Q2:S2"/>
@@ -4990,13 +5370,6 @@
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="U2:W2"/>
-    <mergeCell ref="AF17:AK17"/>
-    <mergeCell ref="AM17:AR17"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="U1:W1"/>
-    <mergeCell ref="Y1:AA1"/>
-    <mergeCell ref="M1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/UniteD-SRL - run.xlsx
+++ b/results/UniteD-SRL - run.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\vito\SRL\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF22AB8D-5115-4C14-850D-AFAD3BA3C1C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D243B2C6-F489-4563-A187-75172E72CF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42165" yWindow="2850" windowWidth="22275" windowHeight="10365" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="42510" yWindow="3195" windowWidth="22275" windowHeight="10965" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dependency-based" sheetId="1" r:id="rId1"/>
@@ -234,6 +234,9 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -246,9 +249,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -511,32 +511,32 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
+      <c r="I1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
       <c r="L1" s="2"/>
-      <c r="M1" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="Q1" s="14" t="s">
+      <c r="M1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="Q1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="U1" s="14" t="s">
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="U1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="Y1" s="14" t="s">
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="Y1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="Z1" s="15"/>
-      <c r="AA1" s="15"/>
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16"/>
       <c r="AB1" s="2"/>
       <c r="AC1" s="2"/>
       <c r="AD1" s="2"/>
@@ -556,44 +556,44 @@
       <c r="AR1" s="2"/>
     </row>
     <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
       <c r="L2" s="2"/>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="Q2" s="17" t="s">
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="Q2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="U2" s="17" t="s">
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="U2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="Y2" s="17" t="s">
+      <c r="V2" s="16"/>
+      <c r="W2" s="16"/>
+      <c r="Y2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
       <c r="AD2" s="2"/>
@@ -613,7 +613,7 @@
       <c r="AR2" s="2"/>
     </row>
     <row r="3" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="15"/>
+      <c r="A3" s="16"/>
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1374,15 +1374,15 @@
         <v>8.5</v>
       </c>
       <c r="Y11" s="6">
-        <f t="shared" ref="Y11:Y17" si="3">AVERAGE(I11,M11,Q11,U11)</f>
+        <f t="shared" ref="Y11:Y16" si="3">AVERAGE(I11,M11,Q11,U11)</f>
         <v>22.72</v>
       </c>
       <c r="Z11" s="6">
-        <f t="shared" ref="Z11:Z17" si="4">AVERAGE(J11,N11,R11,V11)</f>
+        <f t="shared" ref="Z11:Z16" si="4">AVERAGE(J11,N11,R11,V11)</f>
         <v>21.022500000000001</v>
       </c>
       <c r="AA11" s="7">
-        <f t="shared" ref="AA11:AA17" si="5">AVERAGE(K11,O11,S11,W11)</f>
+        <f t="shared" ref="AA11:AA16" si="5">AVERAGE(K11,O11,S11,W11)</f>
         <v>21.82</v>
       </c>
     </row>
@@ -1808,19 +1808,19 @@
       <c r="AC17" s="2"/>
       <c r="AD17" s="2"/>
       <c r="AE17" s="1"/>
-      <c r="AF17" s="14"/>
-      <c r="AG17" s="15"/>
-      <c r="AH17" s="15"/>
-      <c r="AI17" s="15"/>
-      <c r="AJ17" s="15"/>
-      <c r="AK17" s="15"/>
+      <c r="AF17" s="15"/>
+      <c r="AG17" s="16"/>
+      <c r="AH17" s="16"/>
+      <c r="AI17" s="16"/>
+      <c r="AJ17" s="16"/>
+      <c r="AK17" s="16"/>
       <c r="AL17" s="1"/>
-      <c r="AM17" s="14"/>
-      <c r="AN17" s="15"/>
-      <c r="AO17" s="15"/>
-      <c r="AP17" s="15"/>
-      <c r="AQ17" s="15"/>
-      <c r="AR17" s="15"/>
+      <c r="AM17" s="15"/>
+      <c r="AN17" s="16"/>
+      <c r="AO17" s="16"/>
+      <c r="AP17" s="16"/>
+      <c r="AQ17" s="16"/>
+      <c r="AR17" s="16"/>
     </row>
     <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
@@ -1916,30 +1916,54 @@
       <c r="G19" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="7"/>
+      <c r="I19" s="6">
+        <v>29.51</v>
+      </c>
+      <c r="J19" s="6">
+        <v>19.73</v>
+      </c>
+      <c r="K19" s="7">
+        <v>23.65</v>
+      </c>
       <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="7"/>
-      <c r="Q19" s="6"/>
-      <c r="R19" s="6"/>
-      <c r="S19" s="7"/>
-      <c r="U19" s="6"/>
-      <c r="V19" s="6"/>
-      <c r="W19" s="7"/>
-      <c r="Y19" s="6" t="e">
+      <c r="M19" s="6">
+        <v>11.28</v>
+      </c>
+      <c r="N19" s="6">
+        <v>7.16</v>
+      </c>
+      <c r="O19" s="7">
+        <v>8.76</v>
+      </c>
+      <c r="Q19" s="6">
+        <v>28.61</v>
+      </c>
+      <c r="R19" s="6">
+        <v>21.41</v>
+      </c>
+      <c r="S19" s="7">
+        <v>24.49</v>
+      </c>
+      <c r="U19" s="6">
+        <v>28.93</v>
+      </c>
+      <c r="V19" s="6">
+        <v>17.559999999999999</v>
+      </c>
+      <c r="W19" s="7">
+        <v>21.85</v>
+      </c>
+      <c r="Y19" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z19" s="6" t="e">
+        <v>24.582500000000003</v>
+      </c>
+      <c r="Z19" s="6">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA19" s="7" t="e">
+        <v>16.465</v>
+      </c>
+      <c r="AA19" s="7">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>19.6875</v>
       </c>
     </row>
     <row r="20" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2942,32 +2966,32 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
-      <c r="I1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
+      <c r="I1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
       <c r="L1" s="2"/>
-      <c r="M1" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="Q1" s="14" t="s">
+      <c r="M1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="Q1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="U1" s="14" t="s">
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="U1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="Y1" s="14" t="s">
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="Y1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="Z1" s="15"/>
-      <c r="AA1" s="15"/>
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16"/>
       <c r="AB1" s="2"/>
       <c r="AC1" s="2"/>
       <c r="AD1" s="2"/>
@@ -2987,44 +3011,44 @@
       <c r="AR1" s="2"/>
     </row>
     <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
       <c r="L2" s="2"/>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="Q2" s="17" t="s">
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="Q2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="U2" s="17" t="s">
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="U2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="Y2" s="17" t="s">
+      <c r="V2" s="16"/>
+      <c r="W2" s="16"/>
+      <c r="Y2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
+      <c r="Z2" s="16"/>
+      <c r="AA2" s="16"/>
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
       <c r="AD2" s="2"/>
@@ -3044,7 +3068,7 @@
       <c r="AR2" s="2"/>
     </row>
     <row r="3" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="15"/>
+      <c r="A3" s="16"/>
       <c r="B3" s="3" t="s">
         <v>8</v>
       </c>
@@ -4223,7 +4247,7 @@
       <c r="W17" s="7">
         <v>1.74</v>
       </c>
-      <c r="X17" s="19"/>
+      <c r="X17" s="14"/>
       <c r="Y17" s="6">
         <f t="shared" si="1"/>
         <v>6.7224999999999993</v>
@@ -4240,19 +4264,19 @@
       <c r="AC17" s="2"/>
       <c r="AD17" s="2"/>
       <c r="AE17" s="1"/>
-      <c r="AF17" s="14"/>
-      <c r="AG17" s="15"/>
-      <c r="AH17" s="15"/>
-      <c r="AI17" s="15"/>
-      <c r="AJ17" s="15"/>
-      <c r="AK17" s="15"/>
+      <c r="AF17" s="15"/>
+      <c r="AG17" s="16"/>
+      <c r="AH17" s="16"/>
+      <c r="AI17" s="16"/>
+      <c r="AJ17" s="16"/>
+      <c r="AK17" s="16"/>
       <c r="AL17" s="1"/>
-      <c r="AM17" s="14"/>
-      <c r="AN17" s="15"/>
-      <c r="AO17" s="15"/>
-      <c r="AP17" s="15"/>
-      <c r="AQ17" s="15"/>
-      <c r="AR17" s="15"/>
+      <c r="AM17" s="15"/>
+      <c r="AN17" s="16"/>
+      <c r="AO17" s="16"/>
+      <c r="AP17" s="16"/>
+      <c r="AQ17" s="16"/>
+      <c r="AR17" s="16"/>
     </row>
     <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
@@ -4349,54 +4373,54 @@
         <v>1</v>
       </c>
       <c r="I19" s="6">
-        <v>2.0699999999999998</v>
+        <v>29.86</v>
       </c>
       <c r="J19" s="6">
-        <v>0.21</v>
+        <v>16.96</v>
       </c>
       <c r="K19" s="7">
-        <v>0.38</v>
+        <v>21.63</v>
       </c>
       <c r="L19" s="6"/>
       <c r="M19" s="6">
-        <v>5.73</v>
+        <v>39.65</v>
       </c>
       <c r="N19" s="6">
-        <v>0.85</v>
+        <v>15.05</v>
       </c>
       <c r="O19" s="7">
-        <v>1.48</v>
+        <v>21.81</v>
       </c>
       <c r="Q19" s="6">
-        <v>2.3199999999999998</v>
+        <v>27.66</v>
       </c>
       <c r="R19" s="6">
-        <v>0.48</v>
+        <v>15.19</v>
       </c>
       <c r="S19" s="7">
-        <v>0.8</v>
+        <v>19.61</v>
       </c>
       <c r="U19" s="6">
-        <v>1.84</v>
+        <v>29.17</v>
       </c>
       <c r="V19" s="6">
-        <v>0.37</v>
+        <v>14.74</v>
       </c>
       <c r="W19" s="7">
-        <v>0.62</v>
-      </c>
-      <c r="X19" s="19"/>
+        <v>19.579999999999998</v>
+      </c>
+      <c r="X19" s="14"/>
       <c r="Y19" s="6">
         <f t="shared" si="1"/>
-        <v>2.99</v>
+        <v>31.584999999999997</v>
       </c>
       <c r="Z19" s="6">
         <f t="shared" si="1"/>
-        <v>0.47750000000000004</v>
+        <v>15.485000000000001</v>
       </c>
       <c r="AA19" s="7">
         <f t="shared" si="1"/>
-        <v>0.82000000000000006</v>
+        <v>20.657499999999999</v>
       </c>
     </row>
     <row r="20" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5356,6 +5380,13 @@
     <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="Y2:AA2"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="U2:W2"/>
     <mergeCell ref="AF17:AK17"/>
     <mergeCell ref="AM17:AR17"/>
     <mergeCell ref="I1:K1"/>
@@ -5363,13 +5394,6 @@
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="Y1:AA1"/>
     <mergeCell ref="M1:O1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="Y2:AA2"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="U2:W2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/UniteD-SRL - run.xlsx
+++ b/results/UniteD-SRL - run.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\vito\SRL\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lorpa\Documents\Università\Magistrale\Anno2\TESI\project\SRL\SRL\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D243B2C6-F489-4563-A187-75172E72CF4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FA4499-A205-4082-8014-A1E5B1B9EB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42510" yWindow="3195" windowWidth="22275" windowHeight="10965" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dependency-based" sheetId="1" r:id="rId1"/>
@@ -18,17 +18,6 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="O3dul5VTG9qJH6bckBMXuISjKzusumlk/3Xuqo2jwCo="/>
     </ext>
@@ -37,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="21">
   <si>
     <t>English</t>
   </si>
@@ -486,23 +475,23 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AR967"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" customWidth="1"/>
-    <col min="2" max="7" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="21.54296875" customWidth="1"/>
+    <col min="2" max="7" width="7.7265625" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="9" max="11" width="6.42578125" customWidth="1"/>
-    <col min="12" max="12" width="3.85546875" customWidth="1"/>
-    <col min="13" max="15" width="6.42578125" customWidth="1"/>
-    <col min="16" max="16" width="3.85546875" customWidth="1"/>
-    <col min="17" max="19" width="6.42578125" customWidth="1"/>
-    <col min="20" max="20" width="3.85546875" customWidth="1"/>
-    <col min="21" max="23" width="6.42578125" customWidth="1"/>
-    <col min="24" max="24" width="3.85546875" customWidth="1"/>
-    <col min="25" max="44" width="6.42578125" customWidth="1"/>
+    <col min="9" max="11" width="6.453125" customWidth="1"/>
+    <col min="12" max="12" width="3.81640625" customWidth="1"/>
+    <col min="13" max="15" width="6.453125" customWidth="1"/>
+    <col min="16" max="16" width="3.81640625" customWidth="1"/>
+    <col min="17" max="19" width="6.453125" customWidth="1"/>
+    <col min="20" max="20" width="3.81640625" customWidth="1"/>
+    <col min="21" max="23" width="6.453125" customWidth="1"/>
+    <col min="24" max="24" width="3.81640625" customWidth="1"/>
+    <col min="25" max="44" width="6.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -555,7 +544,7 @@
       <c r="AQ1" s="2"/>
       <c r="AR1" s="2"/>
     </row>
-    <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>5</v>
       </c>
@@ -612,7 +601,7 @@
       <c r="AQ2" s="2"/>
       <c r="AR2" s="2"/>
     </row>
-    <row r="3" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="3" t="s">
         <v>8</v>
@@ -697,7 +686,7 @@
       <c r="AQ3" s="2"/>
       <c r="AR3" s="2"/>
     </row>
-    <row r="4" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>17</v>
       </c>
@@ -787,7 +776,7 @@
       <c r="AQ4" s="6"/>
       <c r="AR4" s="6"/>
     </row>
-    <row r="5" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="13" t="b">
         <v>0</v>
@@ -875,7 +864,7 @@
       <c r="AQ5" s="6"/>
       <c r="AR5" s="6"/>
     </row>
-    <row r="6" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="13" t="b">
         <v>1</v>
@@ -963,7 +952,7 @@
       <c r="AQ6" s="6"/>
       <c r="AR6" s="6"/>
     </row>
-    <row r="7" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="13" t="b">
         <v>1</v>
@@ -1051,7 +1040,7 @@
       <c r="AQ7" s="6"/>
       <c r="AR7" s="6"/>
     </row>
-    <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="13" t="b">
         <v>1</v>
@@ -1139,7 +1128,7 @@
       <c r="AQ8" s="6"/>
       <c r="AR8" s="6"/>
     </row>
-    <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="13" t="b">
         <v>1</v>
@@ -1227,7 +1216,7 @@
       <c r="AQ9" s="6"/>
       <c r="AR9" s="6"/>
     </row>
-    <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>18</v>
       </c>
@@ -1317,7 +1306,7 @@
       <c r="AQ10" s="6"/>
       <c r="AR10" s="6"/>
     </row>
-    <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="B11" s="13" t="b">
         <v>0</v>
@@ -1386,7 +1375,7 @@
         <v>21.82</v>
       </c>
     </row>
-    <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="13" t="b">
         <v>1</v>
@@ -1455,7 +1444,7 @@
         <v>52.85</v>
       </c>
     </row>
-    <row r="13" spans="1:44" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:44" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="13" t="b">
         <v>1</v>
@@ -1524,7 +1513,7 @@
         <v>49.817500000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:44" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:44" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="13" t="b">
         <v>1</v>
@@ -1593,7 +1582,7 @@
         <v>64.302500000000009</v>
       </c>
     </row>
-    <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="13" t="b">
         <v>1</v>
@@ -1662,7 +1651,7 @@
         <v>71.377499999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>19</v>
       </c>
@@ -1734,7 +1723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="13" t="b">
         <v>0</v>
@@ -1822,7 +1811,7 @@
       <c r="AQ17" s="16"/>
       <c r="AR17" s="16"/>
     </row>
-    <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>19</v>
       </c>
@@ -1894,7 +1883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>20</v>
       </c>
@@ -1966,954 +1955,1093 @@
         <v>19.6875</v>
       </c>
     </row>
-    <row r="20" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C20" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="7"/>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="7"/>
+      <c r="U20" s="6"/>
+      <c r="V20" s="6"/>
+      <c r="W20" s="7"/>
+      <c r="Y20" s="6" t="e">
+        <f t="shared" ref="Y20:Y21" si="9">AVERAGE(I20,M20,Q20,U20)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z20" s="6" t="e">
+        <f t="shared" ref="Z20:Z21" si="10">AVERAGE(J20,N20,R20,V20)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA20" s="7" t="e">
+        <f t="shared" ref="AA20:AA21" si="11">AVERAGE(K20,O20,S20,W20)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12"/>
+      <c r="B21" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D21" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="7"/>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="6"/>
+      <c r="S21" s="7"/>
+      <c r="U21" s="6"/>
+      <c r="V21" s="6"/>
+      <c r="W21" s="7"/>
+      <c r="Y21" s="6" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z21" s="6" t="e">
+        <f t="shared" si="10"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA21" s="7" t="e">
+        <f t="shared" si="11"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C22" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="7"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="7"/>
+      <c r="U22" s="6"/>
+      <c r="V22" s="6"/>
+      <c r="W22" s="7"/>
+      <c r="Y22" s="6" t="e">
+        <f t="shared" ref="Y22" si="12">AVERAGE(I22,M22,Q22,U22)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z22" s="6" t="e">
+        <f t="shared" ref="Z22" si="13">AVERAGE(J22,N22,R22,V22)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA22" s="7" t="e">
+        <f t="shared" ref="AA22" si="14">AVERAGE(K22,O22,S22,W22)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="AM17:AR17"/>
@@ -2941,23 +3069,23 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AR974"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" customWidth="1"/>
-    <col min="2" max="7" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="21.54296875" customWidth="1"/>
+    <col min="2" max="7" width="7.7265625" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="9" max="11" width="6.42578125" customWidth="1"/>
-    <col min="12" max="12" width="3.85546875" customWidth="1"/>
-    <col min="13" max="15" width="6.42578125" customWidth="1"/>
-    <col min="16" max="16" width="3.85546875" customWidth="1"/>
-    <col min="17" max="19" width="6.42578125" customWidth="1"/>
-    <col min="20" max="20" width="3.85546875" customWidth="1"/>
-    <col min="21" max="23" width="6.42578125" customWidth="1"/>
-    <col min="24" max="24" width="3.85546875" customWidth="1"/>
-    <col min="25" max="44" width="6.42578125" customWidth="1"/>
+    <col min="9" max="11" width="6.453125" customWidth="1"/>
+    <col min="12" max="12" width="3.81640625" customWidth="1"/>
+    <col min="13" max="15" width="6.453125" customWidth="1"/>
+    <col min="16" max="16" width="3.81640625" customWidth="1"/>
+    <col min="17" max="19" width="6.453125" customWidth="1"/>
+    <col min="20" max="20" width="3.81640625" customWidth="1"/>
+    <col min="21" max="23" width="6.453125" customWidth="1"/>
+    <col min="24" max="24" width="3.81640625" customWidth="1"/>
+    <col min="25" max="44" width="6.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3010,7 +3138,7 @@
       <c r="AQ1" s="2"/>
       <c r="AR1" s="2"/>
     </row>
-    <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
         <v>5</v>
       </c>
@@ -3067,7 +3195,7 @@
       <c r="AQ2" s="2"/>
       <c r="AR2" s="2"/>
     </row>
-    <row r="3" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="3" t="s">
         <v>8</v>
@@ -3152,7 +3280,7 @@
       <c r="AQ3" s="2"/>
       <c r="AR3" s="2"/>
     </row>
-    <row r="4" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>17</v>
       </c>
@@ -3242,7 +3370,7 @@
       <c r="AQ4" s="6"/>
       <c r="AR4" s="6"/>
     </row>
-    <row r="5" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="13" t="b">
         <v>0</v>
@@ -3330,7 +3458,7 @@
       <c r="AQ5" s="6"/>
       <c r="AR5" s="6"/>
     </row>
-    <row r="6" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="13" t="b">
         <v>1</v>
@@ -3418,7 +3546,7 @@
       <c r="AQ6" s="6"/>
       <c r="AR6" s="6"/>
     </row>
-    <row r="7" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="13" t="b">
         <v>1</v>
@@ -3506,7 +3634,7 @@
       <c r="AQ7" s="6"/>
       <c r="AR7" s="6"/>
     </row>
-    <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="13" t="b">
         <v>1</v>
@@ -3594,7 +3722,7 @@
       <c r="AQ8" s="6"/>
       <c r="AR8" s="6"/>
     </row>
-    <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="13" t="b">
         <v>1</v>
@@ -3682,7 +3810,7 @@
       <c r="AQ9" s="6"/>
       <c r="AR9" s="6"/>
     </row>
-    <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
         <v>18</v>
       </c>
@@ -3772,7 +3900,7 @@
       <c r="AQ10" s="6"/>
       <c r="AR10" s="6"/>
     </row>
-    <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="B11" s="13" t="b">
         <v>0</v>
@@ -3829,7 +3957,7 @@
         <v>15.7</v>
       </c>
       <c r="Y11" s="6">
-        <f t="shared" ref="Y11:AA19" si="1">AVERAGE(I11,M11,Q11,U11)</f>
+        <f t="shared" ref="Y11:AA22" si="1">AVERAGE(I11,M11,Q11,U11)</f>
         <v>56.392499999999998</v>
       </c>
       <c r="Z11" s="6">
@@ -3841,7 +3969,7 @@
         <v>33.892499999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="13" t="b">
         <v>1</v>
@@ -3910,7 +4038,7 @@
         <v>61.75</v>
       </c>
     </row>
-    <row r="13" spans="1:44" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:44" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="13" t="b">
         <v>1</v>
@@ -3979,7 +4107,7 @@
         <v>64.864999999999995</v>
       </c>
     </row>
-    <row r="14" spans="1:44" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:44" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="13" t="b">
         <v>1</v>
@@ -4048,7 +4176,7 @@
         <v>68.397500000000008</v>
       </c>
     </row>
-    <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="B15" s="13" t="b">
         <v>1</v>
@@ -4117,7 +4245,7 @@
         <v>73.552500000000009</v>
       </c>
     </row>
-    <row r="16" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>19</v>
       </c>
@@ -4189,7 +4317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="12"/>
       <c r="B17" s="13" t="b">
         <v>0</v>
@@ -4278,7 +4406,7 @@
       <c r="AQ17" s="16"/>
       <c r="AR17" s="16"/>
     </row>
-    <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>19</v>
       </c>
@@ -4350,7 +4478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>20</v>
       </c>
@@ -4423,963 +4551,1109 @@
         <v>20.657499999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C20" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="7"/>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="7"/>
+      <c r="U20" s="6"/>
+      <c r="V20" s="6"/>
+      <c r="W20" s="7"/>
+      <c r="Y20" s="6" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z20" s="6" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA20" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12"/>
+      <c r="B21" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D21" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="7"/>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="6"/>
+      <c r="S21" s="7"/>
+      <c r="U21" s="6"/>
+      <c r="V21" s="6"/>
+      <c r="W21" s="7"/>
+      <c r="Y21" s="6" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z21" s="6" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA21" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C22" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="7"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="7"/>
+      <c r="U22" s="6"/>
+      <c r="V22" s="6"/>
+      <c r="W22" s="7"/>
+      <c r="Y22" s="6" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z22" s="6" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA22" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="AF17:AK17"/>
+    <mergeCell ref="AM17:AR17"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="U1:W1"/>
+    <mergeCell ref="Y1:AA1"/>
+    <mergeCell ref="M1:O1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="Q2:S2"/>
@@ -5387,13 +5661,6 @@
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="U2:W2"/>
-    <mergeCell ref="AF17:AK17"/>
-    <mergeCell ref="AM17:AR17"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="U1:W1"/>
-    <mergeCell ref="Y1:AA1"/>
-    <mergeCell ref="M1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/UniteD-SRL - run.xlsx
+++ b/results/UniteD-SRL - run.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lorpa\Documents\Università\Magistrale\Anno2\TESI\project\SRL\SRL\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FA4499-A205-4082-8014-A1E5B1B9EB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8BDAF93-6E5D-4031-9033-059C98D43366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dependency-based" sheetId="1" r:id="rId1"/>
@@ -1977,30 +1977,54 @@
       <c r="G20" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="7"/>
+      <c r="I20" s="6">
+        <v>10</v>
+      </c>
+      <c r="J20" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="K20" s="7">
+        <v>0.02</v>
+      </c>
       <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="7"/>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="6"/>
-      <c r="S20" s="7"/>
-      <c r="U20" s="6"/>
-      <c r="V20" s="6"/>
-      <c r="W20" s="7"/>
-      <c r="Y20" s="6" t="e">
+      <c r="M20" s="6">
+        <v>0</v>
+      </c>
+      <c r="N20" s="6">
+        <v>0</v>
+      </c>
+      <c r="O20" s="7">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="6">
+        <v>2.94</v>
+      </c>
+      <c r="R20" s="6">
+        <v>0</v>
+      </c>
+      <c r="S20" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="U20" s="6">
+        <v>0</v>
+      </c>
+      <c r="V20" s="6">
+        <v>0</v>
+      </c>
+      <c r="W20" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="6">
         <f t="shared" ref="Y20:Y21" si="9">AVERAGE(I20,M20,Q20,U20)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z20" s="6" t="e">
+        <v>3.2349999999999999</v>
+      </c>
+      <c r="Z20" s="6">
         <f t="shared" ref="Z20:Z21" si="10">AVERAGE(J20,N20,R20,V20)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA20" s="7" t="e">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="AA20" s="7">
         <f t="shared" ref="AA20:AA21" si="11">AVERAGE(K20,O20,S20,W20)</f>
-        <v>#DIV/0!</v>
+        <v>7.4999999999999997E-3</v>
       </c>
     </row>
     <row r="21" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2023,30 +2047,54 @@
       <c r="G21" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="7"/>
+      <c r="I21" s="6">
+        <v>0</v>
+      </c>
+      <c r="J21" s="6">
+        <v>0</v>
+      </c>
+      <c r="K21" s="7">
+        <v>0</v>
+      </c>
       <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="6"/>
-      <c r="O21" s="7"/>
-      <c r="Q21" s="6"/>
-      <c r="R21" s="6"/>
-      <c r="S21" s="7"/>
-      <c r="U21" s="6"/>
-      <c r="V21" s="6"/>
-      <c r="W21" s="7"/>
-      <c r="Y21" s="6" t="e">
+      <c r="M21" s="6">
+        <v>3.06</v>
+      </c>
+      <c r="N21" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="O21" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="Q21" s="6">
+        <v>0</v>
+      </c>
+      <c r="R21" s="6">
+        <v>0</v>
+      </c>
+      <c r="S21" s="7">
+        <v>0</v>
+      </c>
+      <c r="U21" s="6">
+        <v>0</v>
+      </c>
+      <c r="V21" s="6">
+        <v>0</v>
+      </c>
+      <c r="W21" s="7">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="6">
         <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z21" s="6" t="e">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="Z21" s="6">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA21" s="7" t="e">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="AA21" s="7">
         <f t="shared" si="11"/>
-        <v>#DIV/0!</v>
+        <v>5.0000000000000001E-3</v>
       </c>
     </row>
     <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2071,35 +2119,320 @@
       <c r="G22" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="7"/>
+      <c r="I22" s="6">
+        <v>4.05</v>
+      </c>
+      <c r="J22" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="K22" s="7">
+        <v>0.19</v>
+      </c>
       <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="7"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="7"/>
-      <c r="U22" s="6"/>
-      <c r="V22" s="6"/>
-      <c r="W22" s="7"/>
-      <c r="Y22" s="6" t="e">
-        <f t="shared" ref="Y22" si="12">AVERAGE(I22,M22,Q22,U22)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z22" s="6" t="e">
-        <f t="shared" ref="Z22" si="13">AVERAGE(J22,N22,R22,V22)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA22" s="7" t="e">
-        <f t="shared" ref="AA22" si="14">AVERAGE(K22,O22,S22,W22)</f>
-        <v>#DIV/0!</v>
+      <c r="M22" s="6">
+        <v>7.03</v>
+      </c>
+      <c r="N22" s="6">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="O22" s="7">
+        <v>0.27</v>
+      </c>
+      <c r="Q22" s="6">
+        <v>5.43</v>
+      </c>
+      <c r="R22" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="S22" s="7">
+        <v>0.17</v>
+      </c>
+      <c r="U22" s="6">
+        <v>3.22</v>
+      </c>
+      <c r="V22" s="6">
+        <v>0</v>
+      </c>
+      <c r="W22" s="7">
+        <v>0.01</v>
+      </c>
+      <c r="Y22" s="6">
+        <f t="shared" ref="Y22:Y25" si="12">AVERAGE(I22,M22,Q22,U22)</f>
+        <v>4.9324999999999992</v>
+      </c>
+      <c r="Z22" s="6">
+        <f t="shared" ref="Z22:Z25" si="13">AVERAGE(J22,N22,R22,V22)</f>
+        <v>0.08</v>
+      </c>
+      <c r="AA22" s="7">
+        <f t="shared" ref="AA22:AA25" si="14">AVERAGE(K22,O22,S22,W22)</f>
+        <v>0.16</v>
       </c>
     </row>
-    <row r="23" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="12"/>
+      <c r="B23" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C23" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D23" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1"/>
+      <c r="I23" s="6">
+        <v>5.82</v>
+      </c>
+      <c r="J23" s="6">
+        <v>0.31</v>
+      </c>
+      <c r="K23" s="7">
+        <v>0.59</v>
+      </c>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6">
+        <v>4.8</v>
+      </c>
+      <c r="N23" s="6">
+        <v>0.22</v>
+      </c>
+      <c r="O23" s="7">
+        <v>0.42</v>
+      </c>
+      <c r="Q23" s="6">
+        <v>14.6</v>
+      </c>
+      <c r="R23" s="6">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="S23" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="U23" s="6">
+        <v>20</v>
+      </c>
+      <c r="V23" s="6">
+        <v>0.12</v>
+      </c>
+      <c r="W23" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="Y23" s="6">
+        <f t="shared" si="12"/>
+        <v>11.305</v>
+      </c>
+      <c r="Z23" s="6">
+        <f t="shared" si="13"/>
+        <v>0.30500000000000005</v>
+      </c>
+      <c r="AA23" s="7">
+        <f t="shared" si="14"/>
+        <v>0.59000000000000008</v>
+      </c>
+      <c r="AB23" s="6"/>
+      <c r="AC23" s="6"/>
+      <c r="AD23" s="6"/>
+      <c r="AE23" s="6"/>
+      <c r="AF23" s="6"/>
+      <c r="AG23" s="6"/>
+      <c r="AH23" s="6"/>
+      <c r="AI23" s="6"/>
+      <c r="AJ23" s="6"/>
+      <c r="AK23" s="6"/>
+      <c r="AL23" s="6"/>
+      <c r="AM23" s="6"/>
+      <c r="AN23" s="6"/>
+      <c r="AO23" s="6"/>
+      <c r="AP23" s="6"/>
+      <c r="AQ23" s="6"/>
+      <c r="AR23" s="6"/>
+    </row>
+    <row r="24" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="12"/>
+      <c r="B24" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D24" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1"/>
+      <c r="I24" s="6">
+        <v>3.73</v>
+      </c>
+      <c r="J24" s="6">
+        <v>0.71</v>
+      </c>
+      <c r="K24" s="7">
+        <v>1.2</v>
+      </c>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6">
+        <v>3.82</v>
+      </c>
+      <c r="N24" s="6">
+        <v>0.49</v>
+      </c>
+      <c r="O24" s="7">
+        <v>0.88</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>7.97</v>
+      </c>
+      <c r="R24" s="6">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="S24" s="7">
+        <v>1.92</v>
+      </c>
+      <c r="U24" s="6">
+        <v>8.9700000000000006</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.71</v>
+      </c>
+      <c r="W24" s="7">
+        <v>1.32</v>
+      </c>
+      <c r="Y24" s="6">
+        <f t="shared" si="12"/>
+        <v>6.1225000000000005</v>
+      </c>
+      <c r="Z24" s="6">
+        <f t="shared" si="13"/>
+        <v>0.75</v>
+      </c>
+      <c r="AA24" s="7">
+        <f t="shared" si="14"/>
+        <v>1.33</v>
+      </c>
+      <c r="AB24" s="6"/>
+      <c r="AC24" s="6"/>
+      <c r="AD24" s="6"/>
+      <c r="AE24" s="6"/>
+      <c r="AF24" s="6"/>
+      <c r="AG24" s="6"/>
+      <c r="AH24" s="6"/>
+      <c r="AI24" s="6"/>
+      <c r="AJ24" s="6"/>
+      <c r="AK24" s="6"/>
+      <c r="AL24" s="6"/>
+      <c r="AM24" s="6"/>
+      <c r="AN24" s="6"/>
+      <c r="AO24" s="6"/>
+      <c r="AP24" s="6"/>
+      <c r="AQ24" s="6"/>
+      <c r="AR24" s="6"/>
+    </row>
+    <row r="25" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="12"/>
+      <c r="B25" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C25" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" s="6">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="J25" s="6">
+        <v>1.29</v>
+      </c>
+      <c r="K25" s="7">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6">
+        <v>4.4800000000000004</v>
+      </c>
+      <c r="N25" s="6">
+        <v>0.24</v>
+      </c>
+      <c r="O25" s="7">
+        <v>0.47</v>
+      </c>
+      <c r="Q25" s="6">
+        <v>14.55</v>
+      </c>
+      <c r="R25" s="6">
+        <v>1.82</v>
+      </c>
+      <c r="S25" s="7">
+        <v>3.24</v>
+      </c>
+      <c r="U25" s="6">
+        <v>15.37</v>
+      </c>
+      <c r="V25" s="6">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="W25" s="7">
+        <v>2.08</v>
+      </c>
+      <c r="Y25" s="6">
+        <f t="shared" si="12"/>
+        <v>10.737500000000001</v>
+      </c>
+      <c r="Z25" s="6">
+        <f t="shared" si="13"/>
+        <v>1.1175000000000002</v>
+      </c>
+      <c r="AA25" s="7">
+        <f t="shared" si="14"/>
+        <v>2.0075000000000003</v>
+      </c>
+      <c r="AB25" s="6"/>
+      <c r="AC25" s="6"/>
+      <c r="AD25" s="6"/>
+      <c r="AE25" s="6"/>
+      <c r="AF25" s="6"/>
+      <c r="AG25" s="6"/>
+      <c r="AH25" s="6"/>
+      <c r="AI25" s="6"/>
+      <c r="AJ25" s="6"/>
+      <c r="AK25" s="6"/>
+      <c r="AL25" s="6"/>
+      <c r="AM25" s="6"/>
+      <c r="AN25" s="6"/>
+      <c r="AO25" s="6"/>
+      <c r="AP25" s="6"/>
+      <c r="AQ25" s="6"/>
+      <c r="AR25" s="6"/>
+    </row>
     <row r="26" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3957,7 +4290,7 @@
         <v>15.7</v>
       </c>
       <c r="Y11" s="6">
-        <f t="shared" ref="Y11:AA22" si="1">AVERAGE(I11,M11,Q11,U11)</f>
+        <f t="shared" ref="Y11:AA25" si="1">AVERAGE(I11,M11,Q11,U11)</f>
         <v>56.392499999999998</v>
       </c>
       <c r="Z11" s="6">
@@ -4573,30 +4906,54 @@
       <c r="G20" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="7"/>
+      <c r="I20" s="6">
+        <v>13.47</v>
+      </c>
+      <c r="J20" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="K20" s="7">
+        <v>0.16</v>
+      </c>
       <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="7"/>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="6"/>
-      <c r="S20" s="7"/>
-      <c r="U20" s="6"/>
-      <c r="V20" s="6"/>
-      <c r="W20" s="7"/>
-      <c r="Y20" s="6" t="e">
+      <c r="M20" s="6">
+        <v>18.59</v>
+      </c>
+      <c r="N20" s="6">
+        <v>0.04</v>
+      </c>
+      <c r="O20" s="7">
+        <v>0.09</v>
+      </c>
+      <c r="Q20" s="6">
+        <v>9.7799999999999994</v>
+      </c>
+      <c r="R20" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="S20" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="U20" s="6">
+        <v>14.28</v>
+      </c>
+      <c r="V20" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="W20" s="7">
+        <v>0.02</v>
+      </c>
+      <c r="Y20" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z20" s="6" t="e">
+        <v>14.030000000000001</v>
+      </c>
+      <c r="Z20" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA20" s="7" t="e">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="AA20" s="7">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>7.7499999999999999E-2</v>
       </c>
     </row>
     <row r="21" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4619,30 +4976,54 @@
       <c r="G21" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="7"/>
+      <c r="I21" s="6">
+        <v>8.83</v>
+      </c>
+      <c r="J21" s="6">
+        <v>0.01</v>
+      </c>
+      <c r="K21" s="7">
+        <v>0.03</v>
+      </c>
       <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="6"/>
-      <c r="O21" s="7"/>
-      <c r="Q21" s="6"/>
-      <c r="R21" s="6"/>
-      <c r="S21" s="7"/>
-      <c r="U21" s="6"/>
-      <c r="V21" s="6"/>
-      <c r="W21" s="7"/>
-      <c r="Y21" s="6" t="e">
+      <c r="M21" s="6">
+        <v>13.85</v>
+      </c>
+      <c r="N21" s="6">
+        <v>0.04</v>
+      </c>
+      <c r="O21" s="7">
+        <v>0.09</v>
+      </c>
+      <c r="Q21" s="6">
+        <v>16.66</v>
+      </c>
+      <c r="R21" s="6">
+        <v>0.06</v>
+      </c>
+      <c r="S21" s="7">
+        <v>0.12</v>
+      </c>
+      <c r="U21" s="6">
+        <v>14.62</v>
+      </c>
+      <c r="V21" s="6">
+        <v>0.09</v>
+      </c>
+      <c r="W21" s="7">
+        <v>0.19</v>
+      </c>
+      <c r="Y21" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z21" s="6" t="e">
+        <v>13.49</v>
+      </c>
+      <c r="Z21" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA21" s="7" t="e">
+        <v>0.05</v>
+      </c>
+      <c r="AA21" s="7">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.1075</v>
       </c>
     </row>
     <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4667,35 +5048,320 @@
       <c r="G22" s="13" t="b">
         <v>0</v>
       </c>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="7"/>
+      <c r="I22" s="6">
+        <v>10.45</v>
+      </c>
+      <c r="J22" s="6">
+        <v>0.34</v>
+      </c>
+      <c r="K22" s="7">
+        <v>0.66</v>
+      </c>
       <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="7"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="7"/>
-      <c r="U22" s="6"/>
-      <c r="V22" s="6"/>
-      <c r="W22" s="7"/>
-      <c r="Y22" s="6" t="e">
+      <c r="M22" s="6">
+        <v>6.02</v>
+      </c>
+      <c r="N22" s="6">
+        <v>0.12</v>
+      </c>
+      <c r="O22" s="7">
+        <v>0.23</v>
+      </c>
+      <c r="Q22" s="6">
+        <v>7.48</v>
+      </c>
+      <c r="R22" s="6">
+        <v>0.17</v>
+      </c>
+      <c r="S22" s="7">
+        <v>0.34</v>
+      </c>
+      <c r="U22" s="6">
+        <v>5.74</v>
+      </c>
+      <c r="V22" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="W22" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="Y22" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z22" s="6" t="e">
+        <v>7.4224999999999994</v>
+      </c>
+      <c r="Z22" s="6">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA22" s="7" t="e">
+        <v>0.17</v>
+      </c>
+      <c r="AA22" s="7">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>0.33250000000000002</v>
       </c>
     </row>
-    <row r="23" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="12"/>
+      <c r="B23" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C23" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D23" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="1"/>
+      <c r="I23" s="6">
+        <v>8.48</v>
+      </c>
+      <c r="J23" s="6">
+        <v>0.52</v>
+      </c>
+      <c r="K23" s="6">
+        <v>0.99</v>
+      </c>
+      <c r="L23" s="6"/>
+      <c r="M23" s="7">
+        <v>6.67</v>
+      </c>
+      <c r="N23" s="6">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="O23" s="7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="Q23" s="6">
+        <v>8.3699999999999992</v>
+      </c>
+      <c r="R23" s="6">
+        <v>0.63</v>
+      </c>
+      <c r="S23" s="7">
+        <v>1.17</v>
+      </c>
+      <c r="U23" s="6">
+        <v>5.79</v>
+      </c>
+      <c r="V23" s="6">
+        <v>0.18</v>
+      </c>
+      <c r="W23" s="7">
+        <v>0.36</v>
+      </c>
+      <c r="Y23" s="6">
+        <f t="shared" si="1"/>
+        <v>7.3274999999999997</v>
+      </c>
+      <c r="Z23" s="6">
+        <f t="shared" si="1"/>
+        <v>0.40499999999999997</v>
+      </c>
+      <c r="AA23" s="7">
+        <f t="shared" si="1"/>
+        <v>0.76749999999999996</v>
+      </c>
+      <c r="AB23" s="6"/>
+      <c r="AC23" s="6"/>
+      <c r="AD23" s="6"/>
+      <c r="AE23" s="6"/>
+      <c r="AF23" s="6"/>
+      <c r="AG23" s="6"/>
+      <c r="AH23" s="6"/>
+      <c r="AI23" s="6"/>
+      <c r="AJ23" s="6"/>
+      <c r="AK23" s="6"/>
+      <c r="AL23" s="6"/>
+      <c r="AM23" s="6"/>
+      <c r="AN23" s="6"/>
+      <c r="AO23" s="6"/>
+      <c r="AP23" s="6"/>
+      <c r="AQ23" s="6"/>
+      <c r="AR23" s="6"/>
+    </row>
+    <row r="24" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="12"/>
+      <c r="B24" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D24" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" s="13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1"/>
+      <c r="I24" s="6">
+        <v>6.87</v>
+      </c>
+      <c r="J24" s="6">
+        <v>1.07</v>
+      </c>
+      <c r="K24" s="7">
+        <v>1.85</v>
+      </c>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6">
+        <v>2.59</v>
+      </c>
+      <c r="N24" s="6">
+        <v>0.26</v>
+      </c>
+      <c r="O24" s="7">
+        <v>0.47</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>7.99</v>
+      </c>
+      <c r="R24" s="6">
+        <v>1.35</v>
+      </c>
+      <c r="S24" s="7">
+        <v>2.31</v>
+      </c>
+      <c r="U24" s="6">
+        <v>5.46</v>
+      </c>
+      <c r="V24" s="6">
+        <v>0.61</v>
+      </c>
+      <c r="W24" s="7">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="Y24" s="6">
+        <f t="shared" si="1"/>
+        <v>5.7275000000000009</v>
+      </c>
+      <c r="Z24" s="6">
+        <f t="shared" si="1"/>
+        <v>0.82250000000000001</v>
+      </c>
+      <c r="AA24" s="7">
+        <f t="shared" si="1"/>
+        <v>1.4325000000000001</v>
+      </c>
+      <c r="AB24" s="6"/>
+      <c r="AC24" s="6"/>
+      <c r="AD24" s="6"/>
+      <c r="AE24" s="6"/>
+      <c r="AF24" s="6"/>
+      <c r="AG24" s="6"/>
+      <c r="AH24" s="6"/>
+      <c r="AI24" s="6"/>
+      <c r="AJ24" s="6"/>
+      <c r="AK24" s="6"/>
+      <c r="AL24" s="6"/>
+      <c r="AM24" s="6"/>
+      <c r="AN24" s="6"/>
+      <c r="AO24" s="6"/>
+      <c r="AP24" s="6"/>
+      <c r="AQ24" s="6"/>
+      <c r="AR24" s="6"/>
+    </row>
+    <row r="25" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="12"/>
+      <c r="B25" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="C25" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" s="13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" s="6">
+        <v>8.39</v>
+      </c>
+      <c r="J25" s="6">
+        <v>0.93</v>
+      </c>
+      <c r="K25" s="7">
+        <v>1.68</v>
+      </c>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6">
+        <v>4.24</v>
+      </c>
+      <c r="N25" s="6">
+        <v>0.27</v>
+      </c>
+      <c r="O25" s="7">
+        <v>0.51</v>
+      </c>
+      <c r="Q25" s="6">
+        <v>8.4</v>
+      </c>
+      <c r="R25" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="S25" s="7">
+        <v>1.95</v>
+      </c>
+      <c r="U25" s="6">
+        <v>7.09</v>
+      </c>
+      <c r="V25" s="6">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="W25" s="7">
+        <v>1.05</v>
+      </c>
+      <c r="Y25" s="6">
+        <f t="shared" si="1"/>
+        <v>7.03</v>
+      </c>
+      <c r="Z25" s="6">
+        <f t="shared" si="1"/>
+        <v>0.71750000000000003</v>
+      </c>
+      <c r="AA25" s="7">
+        <f t="shared" si="1"/>
+        <v>1.2974999999999999</v>
+      </c>
+      <c r="AB25" s="6"/>
+      <c r="AC25" s="6"/>
+      <c r="AD25" s="6"/>
+      <c r="AE25" s="6"/>
+      <c r="AF25" s="6"/>
+      <c r="AG25" s="6"/>
+      <c r="AH25" s="6"/>
+      <c r="AI25" s="6"/>
+      <c r="AJ25" s="6"/>
+      <c r="AK25" s="6"/>
+      <c r="AL25" s="6"/>
+      <c r="AM25" s="6"/>
+      <c r="AN25" s="6"/>
+      <c r="AO25" s="6"/>
+      <c r="AP25" s="6"/>
+      <c r="AQ25" s="6"/>
+      <c r="AR25" s="6"/>
+    </row>
     <row r="26" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5647,6 +6313,13 @@
     <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="Y2:AA2"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="U2:W2"/>
     <mergeCell ref="AF17:AK17"/>
     <mergeCell ref="AM17:AR17"/>
     <mergeCell ref="I1:K1"/>
@@ -5654,13 +6327,6 @@
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="Y1:AA1"/>
     <mergeCell ref="M1:O1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="Y2:AA2"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="U2:W2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/UniteD-SRL - run.xlsx
+++ b/results/UniteD-SRL - run.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lorpa\Documents\Università\Magistrale\Anno2\TESI\project\SRL\SRL\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8BDAF93-6E5D-4031-9033-059C98D43366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9984A74-BB74-4E87-AEAA-03BE9CAEA0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dependency-based" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="21">
   <si>
     <t>English</t>
   </si>
@@ -1812,9 +1812,7 @@
       <c r="AR17" s="16"/>
     </row>
     <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
-        <v>19</v>
-      </c>
+      <c r="A18" s="11"/>
       <c r="B18" s="13" t="b">
         <v>0</v>
       </c>
@@ -2098,9 +2096,7 @@
       </c>
     </row>
     <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
-        <v>19</v>
-      </c>
+      <c r="A22" s="11"/>
       <c r="B22" s="13" t="b">
         <v>1</v>
       </c>
@@ -4740,9 +4736,7 @@
       <c r="AR17" s="16"/>
     </row>
     <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
-        <v>19</v>
-      </c>
+      <c r="A18" s="11"/>
       <c r="B18" s="13" t="b">
         <v>0</v>
       </c>
@@ -5027,9 +5021,7 @@
       </c>
     </row>
     <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
-        <v>19</v>
-      </c>
+      <c r="A22" s="11"/>
       <c r="B22" s="13" t="b">
         <v>1</v>
       </c>
@@ -6313,6 +6305,13 @@
     <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="AF17:AK17"/>
+    <mergeCell ref="AM17:AR17"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="Q1:S1"/>
+    <mergeCell ref="U1:W1"/>
+    <mergeCell ref="Y1:AA1"/>
+    <mergeCell ref="M1:O1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="Q2:S2"/>
@@ -6320,13 +6319,6 @@
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="U2:W2"/>
-    <mergeCell ref="AF17:AK17"/>
-    <mergeCell ref="AM17:AR17"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="Q1:S1"/>
-    <mergeCell ref="U1:W1"/>
-    <mergeCell ref="Y1:AA1"/>
-    <mergeCell ref="M1:O1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
